--- a/worklog/v2.2.3/s10/pjm/v3/test/ods_risk_measure_v2.xlsx
+++ b/worklog/v2.2.3/s10/pjm/v3/test/ods_risk_measure_v2.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
   <si>
     <t>项目编号</t>
   </si>
@@ -622,163 +622,154 @@
     <t>共检查127条需求</t>
   </si>
   <si>
+    <t>郭伟</t>
+  </si>
+  <si>
+    <t>2025/01/10</t>
+  </si>
+  <si>
+    <t>PJ-2025-003</t>
+  </si>
+  <si>
+    <t>2025-4-10</t>
+  </si>
+  <si>
+    <t>李雪</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>PJ-2025-008</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>钱海</t>
+  </si>
+  <si>
+    <t>2025年2月15日</t>
+  </si>
+  <si>
+    <t>黄磊</t>
+  </si>
+  <si>
+    <t>PJ-2025-007</t>
+  </si>
+  <si>
+    <t>2025-04</t>
+  </si>
+  <si>
     <t>王鹏</t>
   </si>
   <si>
-    <t>PJ-2025-008</t>
-  </si>
-  <si>
-    <t>2025.1.15</t>
-  </si>
-  <si>
-    <t>李雪</t>
-  </si>
-  <si>
-    <t>2025年4月10日</t>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>20250/03/15</t>
+  </si>
+  <si>
+    <t>赵敏</t>
   </si>
   <si>
     <t>PJ-2025-004</t>
   </si>
   <si>
-    <t>2025-03</t>
-  </si>
-  <si>
-    <t>赵敏</t>
-  </si>
-  <si>
-    <t>2025/2/15</t>
+    <t>2025-3-20</t>
+  </si>
+  <si>
+    <t>PJ-2025-006</t>
+  </si>
+  <si>
+    <t>20250/09/30</t>
+  </si>
+  <si>
+    <t>20205/02/15</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025年04月10日</t>
+  </si>
+  <si>
+    <t>20250/04/05</t>
+  </si>
+  <si>
+    <t>2025年1月15日</t>
+  </si>
+  <si>
+    <t>2025-03-32</t>
+  </si>
+  <si>
+    <t>周强</t>
+  </si>
+  <si>
+    <t>2025-3-1</t>
+  </si>
+  <si>
+    <t>2025年9月30日</t>
+  </si>
+  <si>
+    <t>2025/4/10</t>
+  </si>
+  <si>
+    <t>2025/4/5</t>
+  </si>
+  <si>
+    <t>秦川</t>
+  </si>
+  <si>
+    <t>PJ-2025-005</t>
+  </si>
+  <si>
+    <t>2025/02/01</t>
+  </si>
+  <si>
+    <t>2025-13-10</t>
+  </si>
+  <si>
+    <t>2025-02-30</t>
+  </si>
+  <si>
+    <t>2025年3月31日</t>
+  </si>
+  <si>
+    <t>2025.1.10</t>
+  </si>
+  <si>
+    <t>2025-13-30</t>
+  </si>
+  <si>
+    <t>2025-3-10</t>
+  </si>
+  <si>
+    <t>2025-13-15</t>
+  </si>
+  <si>
+    <t>2025-1-25</t>
+  </si>
+  <si>
+    <t>2025/1/10</t>
+  </si>
+  <si>
+    <t>2025.4.30</t>
   </si>
   <si>
     <t>2025-04-32</t>
   </si>
   <si>
-    <t>郭伟</t>
-  </si>
-  <si>
-    <t>周强</t>
-  </si>
-  <si>
-    <t>PJ-2025-003</t>
+    <t>2025-06</t>
   </si>
   <si>
     <t>2025年03月20日</t>
   </si>
   <si>
-    <t>未知</t>
-  </si>
-  <si>
-    <t>钱海</t>
-  </si>
-  <si>
-    <t>秦川</t>
-  </si>
-  <si>
-    <t>PJ-2025-005</t>
-  </si>
-  <si>
-    <t>PJ-2025-007</t>
-  </si>
-  <si>
-    <t>2025-13-10</t>
-  </si>
-  <si>
-    <t>PJ-2025-006</t>
-  </si>
-  <si>
-    <t>20250/03/31</t>
-  </si>
-  <si>
-    <t>待定</t>
-  </si>
-  <si>
-    <t>2025.4.8</t>
-  </si>
-  <si>
-    <t>2025-02-32</t>
-  </si>
-  <si>
-    <t>2025/03/20</t>
-  </si>
-  <si>
-    <t>2025/4/10</t>
-  </si>
-  <si>
-    <t>2025年07月31日</t>
-  </si>
-  <si>
-    <t>2025/04/05</t>
-  </si>
-  <si>
-    <t>2025-13-18</t>
-  </si>
-  <si>
-    <t>2025-1-10</t>
-  </si>
-  <si>
-    <t>2025-02-30</t>
-  </si>
-  <si>
-    <t>20250/03/01</t>
-  </si>
-  <si>
-    <t>20250/09/30</t>
-  </si>
-  <si>
-    <t>20250/04/10</t>
-  </si>
-  <si>
-    <t>2025/3/25</t>
-  </si>
-  <si>
-    <t>20205/04/10</t>
-  </si>
-  <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>2025年04月10日</t>
-  </si>
-  <si>
-    <t>TBD</t>
-  </si>
-  <si>
-    <t>2025.4.10</t>
-  </si>
-  <si>
-    <t>2025-02</t>
-  </si>
-  <si>
-    <t>20250/04/05</t>
-  </si>
-  <si>
-    <t>2025.1.10</t>
-  </si>
-  <si>
-    <t>2025-13-15</t>
-  </si>
-  <si>
-    <t>2025-04</t>
-  </si>
-  <si>
-    <t>2025-03-32</t>
-  </si>
-  <si>
-    <t>2025-4-10</t>
-  </si>
-  <si>
-    <t>2025-06</t>
-  </si>
-  <si>
-    <t>2025年9月30日</t>
-  </si>
-  <si>
-    <t>20205/02/15</t>
-  </si>
-  <si>
-    <t>2025-7-31</t>
-  </si>
-  <si>
-    <t>2025年04月05日</t>
+    <t>2025-05</t>
+  </si>
+  <si>
+    <t>2025年03月18日</t>
   </si>
 </sst>
 </file>
@@ -2196,7 +2187,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
         <v>43</v>
@@ -2211,7 +2202,7 @@
         <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
         <v>48</v>
@@ -2324,7 +2315,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
         <v>43</v>
@@ -2339,7 +2330,7 @@
         <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>205</v>
       </c>
       <c r="G13" t="s">
         <v>48</v>
@@ -2414,7 +2405,7 @@
         <v>84</v>
       </c>
       <c r="AE13" t="s">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="AF13" t="s">
         <v>58</v>
@@ -2447,12 +2438,12 @@
         <v>90</v>
       </c>
       <c r="AP13" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
         <v>91</v>
@@ -2503,7 +2494,7 @@
         <v>48</v>
       </c>
       <c r="R14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S14" t="s">
         <v>60</v>
@@ -2575,12 +2566,12 @@
         <v>110</v>
       </c>
       <c r="AP14" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>209</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
@@ -2595,7 +2586,7 @@
         <v>94</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>209</v>
       </c>
       <c r="G15" t="s">
         <v>96</v>
@@ -2670,7 +2661,7 @@
         <v>114</v>
       </c>
       <c r="AE15" t="s">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="AF15" t="s">
         <v>116</v>
@@ -2703,12 +2694,12 @@
         <v>118</v>
       </c>
       <c r="AP15" t="s">
-        <v>211</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="B16" t="s">
         <v>120</v>
@@ -2723,7 +2714,7 @@
         <v>123</v>
       </c>
       <c r="F16" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s">
         <v>125</v>
@@ -2798,7 +2789,7 @@
         <v>136</v>
       </c>
       <c r="AE16" t="s">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="AF16" t="s">
         <v>96</v>
@@ -2822,7 +2813,7 @@
         <v>56</v>
       </c>
       <c r="AM16" t="s">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="AN16" t="s">
         <v>60</v>
@@ -2831,12 +2822,12 @@
         <v>140</v>
       </c>
       <c r="AP16" t="s">
-        <v>133</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
         <v>120</v>
@@ -2851,7 +2842,7 @@
         <v>123</v>
       </c>
       <c r="F17" t="s">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="G17" t="s">
         <v>125</v>
@@ -2887,7 +2878,7 @@
         <v>131</v>
       </c>
       <c r="R17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="S17" t="s">
         <v>60</v>
@@ -2959,12 +2950,12 @@
         <v>146</v>
       </c>
       <c r="AP17" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
         <v>147</v>
@@ -3087,12 +3078,12 @@
         <v>160</v>
       </c>
       <c r="AP18" t="s">
-        <v>214</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
         <v>161</v>
@@ -3182,7 +3173,7 @@
         <v>176</v>
       </c>
       <c r="AE19" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="AF19" t="s">
         <v>74</v>
@@ -3206,7 +3197,7 @@
         <v>177</v>
       </c>
       <c r="AM19" t="s">
-        <v>59</v>
+        <v>216</v>
       </c>
       <c r="AN19" t="s">
         <v>60</v>
@@ -3215,12 +3206,12 @@
         <v>56</v>
       </c>
       <c r="AP19" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="B20" t="s">
         <v>178</v>
@@ -3334,7 +3325,7 @@
         <v>56</v>
       </c>
       <c r="AM20" t="s">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="AN20" t="s">
         <v>74</v>
@@ -3343,12 +3334,12 @@
         <v>191</v>
       </c>
       <c r="AP20" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s">
         <v>192</v>
@@ -3399,7 +3390,7 @@
         <v>170</v>
       </c>
       <c r="R21" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="S21" t="s">
         <v>116</v>
@@ -3447,7 +3438,7 @@
         <v>72</v>
       </c>
       <c r="AH21" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="AI21" t="s">
         <v>116</v>
@@ -3471,7 +3462,7 @@
         <v>203</v>
       </c>
       <c r="AP21" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22">
@@ -3599,12 +3590,12 @@
         <v>77</v>
       </c>
       <c r="AP22" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
@@ -3727,12 +3718,12 @@
         <v>90</v>
       </c>
       <c r="AP23" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s">
         <v>91</v>
@@ -3783,7 +3774,7 @@
         <v>48</v>
       </c>
       <c r="R24" t="s">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="S24" t="s">
         <v>60</v>
@@ -3822,7 +3813,7 @@
         <v>69</v>
       </c>
       <c r="AE24" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="AF24" t="s">
         <v>80</v>
@@ -3860,7 +3851,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
         <v>91</v>
@@ -3950,7 +3941,7 @@
         <v>114</v>
       </c>
       <c r="AE25" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="AF25" t="s">
         <v>116</v>
@@ -3983,12 +3974,12 @@
         <v>118</v>
       </c>
       <c r="AP25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s">
         <v>120</v>
@@ -4024,7 +4015,7 @@
         <v>126</v>
       </c>
       <c r="M26" t="s">
-        <v>127</v>
+        <v>224</v>
       </c>
       <c r="N26" t="s">
         <v>128</v>
@@ -4111,12 +4102,12 @@
         <v>140</v>
       </c>
       <c r="AP26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
         <v>120</v>
@@ -4131,7 +4122,7 @@
         <v>123</v>
       </c>
       <c r="F27" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="G27" t="s">
         <v>125</v>
@@ -4152,7 +4143,7 @@
         <v>141</v>
       </c>
       <c r="M27" t="s">
-        <v>127</v>
+        <v>226</v>
       </c>
       <c r="N27" t="s">
         <v>56</v>
@@ -4206,7 +4197,7 @@
         <v>136</v>
       </c>
       <c r="AE27" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="AF27" t="s">
         <v>74</v>
@@ -4230,7 +4221,7 @@
         <v>145</v>
       </c>
       <c r="AM27" t="s">
-        <v>59</v>
+        <v>227</v>
       </c>
       <c r="AN27" t="s">
         <v>60</v>
@@ -4239,12 +4230,12 @@
         <v>146</v>
       </c>
       <c r="AP27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B28" t="s">
         <v>147</v>
@@ -4367,12 +4358,12 @@
         <v>160</v>
       </c>
       <c r="AP28" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
         <v>161</v>
@@ -4486,7 +4477,7 @@
         <v>177</v>
       </c>
       <c r="AM29" t="s">
-        <v>223</v>
+        <v>59</v>
       </c>
       <c r="AN29" t="s">
         <v>60</v>
@@ -4495,12 +4486,12 @@
         <v>56</v>
       </c>
       <c r="AP29" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>178</v>
@@ -4623,12 +4614,12 @@
         <v>191</v>
       </c>
       <c r="AP30" t="s">
-        <v>207</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s">
         <v>192</v>
@@ -4664,7 +4655,7 @@
         <v>196</v>
       </c>
       <c r="M31" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="N31" t="s">
         <v>56</v>
@@ -4751,12 +4742,12 @@
         <v>203</v>
       </c>
       <c r="AP31" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -4855,7 +4846,7 @@
         <v>72</v>
       </c>
       <c r="AH32" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="AI32" t="s">
         <v>74</v>
@@ -4879,12 +4870,12 @@
         <v>77</v>
       </c>
       <c r="AP32" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s">
         <v>43</v>
@@ -4974,7 +4965,7 @@
         <v>84</v>
       </c>
       <c r="AE33" t="s">
-        <v>85</v>
+        <v>229</v>
       </c>
       <c r="AF33" t="s">
         <v>58</v>
@@ -4998,7 +4989,7 @@
         <v>56</v>
       </c>
       <c r="AM33" t="s">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="AN33" t="s">
         <v>87</v>
@@ -5007,12 +4998,12 @@
         <v>90</v>
       </c>
       <c r="AP33" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
         <v>91</v>
@@ -5102,7 +5093,7 @@
         <v>69</v>
       </c>
       <c r="AE34" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="AF34" t="s">
         <v>80</v>
@@ -5135,12 +5126,12 @@
         <v>110</v>
       </c>
       <c r="AP34" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
         <v>91</v>
@@ -5155,7 +5146,7 @@
         <v>94</v>
       </c>
       <c r="F35" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="G35" t="s">
         <v>96</v>
@@ -5230,7 +5221,7 @@
         <v>114</v>
       </c>
       <c r="AE35" t="s">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="AF35" t="s">
         <v>116</v>
@@ -5263,12 +5254,12 @@
         <v>118</v>
       </c>
       <c r="AP35" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>223</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
@@ -5382,7 +5373,7 @@
         <v>56</v>
       </c>
       <c r="AM36" t="s">
-        <v>227</v>
+        <v>138</v>
       </c>
       <c r="AN36" t="s">
         <v>60</v>
@@ -5391,7 +5382,7 @@
         <v>140</v>
       </c>
       <c r="AP36" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37">
@@ -5411,7 +5402,7 @@
         <v>123</v>
       </c>
       <c r="F37" t="s">
-        <v>228</v>
+        <v>124</v>
       </c>
       <c r="G37" t="s">
         <v>125</v>
@@ -5432,7 +5423,7 @@
         <v>141</v>
       </c>
       <c r="M37" t="s">
-        <v>127</v>
+        <v>233</v>
       </c>
       <c r="N37" t="s">
         <v>56</v>
@@ -5519,12 +5510,12 @@
         <v>146</v>
       </c>
       <c r="AP37" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B38" t="s">
         <v>147</v>
@@ -5539,7 +5530,7 @@
         <v>149</v>
       </c>
       <c r="F38" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="G38" t="s">
         <v>116</v>
@@ -5575,7 +5566,7 @@
         <v>48</v>
       </c>
       <c r="R38" t="s">
-        <v>230</v>
+        <v>59</v>
       </c>
       <c r="S38" t="s">
         <v>60</v>
@@ -5638,7 +5629,7 @@
         <v>159</v>
       </c>
       <c r="AM38" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="AN38" t="s">
         <v>60</v>
@@ -5647,12 +5638,12 @@
         <v>160</v>
       </c>
       <c r="AP38" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s">
         <v>161</v>
@@ -5667,7 +5658,7 @@
         <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>144</v>
+        <v>56</v>
       </c>
       <c r="G39" t="s">
         <v>74</v>
@@ -5688,7 +5679,7 @@
         <v>166</v>
       </c>
       <c r="M39" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="N39" t="s">
         <v>168</v>
@@ -5742,7 +5733,7 @@
         <v>176</v>
       </c>
       <c r="AE39" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="AF39" t="s">
         <v>74</v>
@@ -5775,12 +5766,12 @@
         <v>56</v>
       </c>
       <c r="AP39" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s">
         <v>178</v>
@@ -5879,7 +5870,7 @@
         <v>72</v>
       </c>
       <c r="AH40" t="s">
-        <v>232</v>
+        <v>73</v>
       </c>
       <c r="AI40" t="s">
         <v>74</v>
@@ -5903,12 +5894,12 @@
         <v>191</v>
       </c>
       <c r="AP40" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B41" t="s">
         <v>192</v>
@@ -5944,7 +5935,7 @@
         <v>196</v>
       </c>
       <c r="M41" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="N41" t="s">
         <v>56</v>
@@ -6022,7 +6013,7 @@
         <v>56</v>
       </c>
       <c r="AM41" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="AN41" t="s">
         <v>116</v>
@@ -6031,12 +6022,12 @@
         <v>203</v>
       </c>
       <c r="AP41" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B42" t="s">
         <v>43</v>
@@ -6126,7 +6117,7 @@
         <v>69</v>
       </c>
       <c r="AE42" t="s">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="AF42" t="s">
         <v>71</v>
@@ -6135,7 +6126,7 @@
         <v>72</v>
       </c>
       <c r="AH42" t="s">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="AI42" t="s">
         <v>74</v>
@@ -6159,12 +6150,12 @@
         <v>77</v>
       </c>
       <c r="AP42" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
         <v>43</v>
@@ -6179,7 +6170,7 @@
         <v>46</v>
       </c>
       <c r="F43" t="s">
-        <v>234</v>
+        <v>47</v>
       </c>
       <c r="G43" t="s">
         <v>48</v>
@@ -6200,7 +6191,7 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>235</v>
+        <v>54</v>
       </c>
       <c r="N43" t="s">
         <v>56</v>
@@ -6287,12 +6278,12 @@
         <v>90</v>
       </c>
       <c r="AP43" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="B44" t="s">
         <v>91</v>
@@ -6307,7 +6298,7 @@
         <v>94</v>
       </c>
       <c r="F44" t="s">
-        <v>236</v>
+        <v>95</v>
       </c>
       <c r="G44" t="s">
         <v>96</v>
@@ -6406,7 +6397,7 @@
         <v>109</v>
       </c>
       <c r="AM44" t="s">
-        <v>59</v>
+        <v>239</v>
       </c>
       <c r="AN44" t="s">
         <v>60</v>
@@ -6415,12 +6406,12 @@
         <v>110</v>
       </c>
       <c r="AP44" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s">
         <v>91</v>
@@ -6471,7 +6462,7 @@
         <v>48</v>
       </c>
       <c r="R45" t="s">
-        <v>230</v>
+        <v>59</v>
       </c>
       <c r="S45" t="s">
         <v>60</v>
@@ -6519,7 +6510,7 @@
         <v>72</v>
       </c>
       <c r="AH45" t="s">
-        <v>73</v>
+        <v>235</v>
       </c>
       <c r="AI45" t="s">
         <v>74</v>
@@ -6534,7 +6525,7 @@
         <v>56</v>
       </c>
       <c r="AM45" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="AN45" t="s">
         <v>74</v>
@@ -6543,12 +6534,12 @@
         <v>118</v>
       </c>
       <c r="AP45" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
         <v>120</v>
@@ -6584,7 +6575,7 @@
         <v>126</v>
       </c>
       <c r="M46" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="N46" t="s">
         <v>128</v>
@@ -6599,7 +6590,7 @@
         <v>131</v>
       </c>
       <c r="R46" t="s">
-        <v>238</v>
+        <v>59</v>
       </c>
       <c r="S46" t="s">
         <v>60</v>
@@ -6671,12 +6662,12 @@
         <v>140</v>
       </c>
       <c r="AP46" t="s">
-        <v>62</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s">
         <v>120</v>
@@ -6799,12 +6790,12 @@
         <v>146</v>
       </c>
       <c r="AP47" t="s">
-        <v>186</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B48" t="s">
         <v>147</v>
@@ -6894,7 +6885,7 @@
         <v>66</v>
       </c>
       <c r="AE48" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="AF48" t="s">
         <v>158</v>
@@ -6927,12 +6918,12 @@
         <v>160</v>
       </c>
       <c r="AP48" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
         <v>161</v>
@@ -7046,7 +7037,7 @@
         <v>177</v>
       </c>
       <c r="AM49" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="AN49" t="s">
         <v>60</v>
@@ -7055,12 +7046,12 @@
         <v>56</v>
       </c>
       <c r="AP49" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
         <v>178</v>
@@ -7150,7 +7141,7 @@
         <v>66</v>
       </c>
       <c r="AE50" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="AF50" t="s">
         <v>116</v>
@@ -7183,7 +7174,7 @@
         <v>191</v>
       </c>
       <c r="AP50" t="s">
-        <v>103</v>
+        <v>204</v>
       </c>
     </row>
     <row r="51">
@@ -7224,7 +7215,7 @@
         <v>196</v>
       </c>
       <c r="M51" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="N51" t="s">
         <v>56</v>
@@ -7311,12 +7302,12 @@
         <v>203</v>
       </c>
       <c r="AP51" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>221</v>
+        <v>42</v>
       </c>
       <c r="B52" t="s">
         <v>43</v>
@@ -7352,7 +7343,7 @@
         <v>53</v>
       </c>
       <c r="M52" t="s">
-        <v>218</v>
+        <v>54</v>
       </c>
       <c r="N52" t="s">
         <v>55</v>
@@ -7367,7 +7358,7 @@
         <v>58</v>
       </c>
       <c r="R52" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="S52" t="s">
         <v>60</v>
@@ -7406,7 +7397,7 @@
         <v>69</v>
       </c>
       <c r="AE52" t="s">
-        <v>243</v>
+        <v>70</v>
       </c>
       <c r="AF52" t="s">
         <v>71</v>
@@ -7444,7 +7435,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="B53" t="s">
         <v>43</v>
@@ -7495,7 +7486,7 @@
         <v>58</v>
       </c>
       <c r="R53" t="s">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="S53" t="s">
         <v>80</v>
@@ -7567,12 +7558,12 @@
         <v>90</v>
       </c>
       <c r="AP53" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B54" t="s">
         <v>91</v>
@@ -7587,7 +7578,7 @@
         <v>94</v>
       </c>
       <c r="F54" t="s">
-        <v>95</v>
+        <v>232</v>
       </c>
       <c r="G54" t="s">
         <v>96</v>
@@ -7623,7 +7614,7 @@
         <v>48</v>
       </c>
       <c r="R54" t="s">
-        <v>230</v>
+        <v>59</v>
       </c>
       <c r="S54" t="s">
         <v>60</v>
@@ -7695,7 +7686,7 @@
         <v>110</v>
       </c>
       <c r="AP54" t="s">
-        <v>62</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55">
@@ -7799,7 +7790,7 @@
         <v>72</v>
       </c>
       <c r="AH55" t="s">
-        <v>73</v>
+        <v>211</v>
       </c>
       <c r="AI55" t="s">
         <v>74</v>
@@ -7814,7 +7805,7 @@
         <v>56</v>
       </c>
       <c r="AM55" t="s">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="AN55" t="s">
         <v>74</v>
@@ -7828,7 +7819,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>119</v>
       </c>
       <c r="B56" t="s">
         <v>120</v>
@@ -7879,7 +7870,7 @@
         <v>131</v>
       </c>
       <c r="R56" t="s">
-        <v>244</v>
+        <v>59</v>
       </c>
       <c r="S56" t="s">
         <v>60</v>
@@ -7918,7 +7909,7 @@
         <v>136</v>
       </c>
       <c r="AE56" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="AF56" t="s">
         <v>96</v>
@@ -7951,12 +7942,12 @@
         <v>140</v>
       </c>
       <c r="AP56" t="s">
-        <v>103</v>
+        <v>236</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>216</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
         <v>120</v>
@@ -7971,7 +7962,7 @@
         <v>123</v>
       </c>
       <c r="F57" t="s">
-        <v>245</v>
+        <v>124</v>
       </c>
       <c r="G57" t="s">
         <v>125</v>
@@ -7992,7 +7983,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s">
-        <v>127</v>
+        <v>240</v>
       </c>
       <c r="N57" t="s">
         <v>56</v>
@@ -8007,7 +7998,7 @@
         <v>131</v>
       </c>
       <c r="R57" t="s">
-        <v>230</v>
+        <v>59</v>
       </c>
       <c r="S57" t="s">
         <v>60</v>
@@ -8079,12 +8070,12 @@
         <v>146</v>
       </c>
       <c r="AP57" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B58" t="s">
         <v>147</v>
@@ -8207,12 +8198,12 @@
         <v>160</v>
       </c>
       <c r="AP58" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B59" t="s">
         <v>161</v>
@@ -8335,12 +8326,12 @@
         <v>56</v>
       </c>
       <c r="AP59" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B60" t="s">
         <v>178</v>
@@ -8463,12 +8454,12 @@
         <v>191</v>
       </c>
       <c r="AP60" t="s">
-        <v>133</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="B61" t="s">
         <v>192</v>
@@ -8504,7 +8495,7 @@
         <v>196</v>
       </c>
       <c r="M61" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="N61" t="s">
         <v>56</v>
@@ -8591,12 +8582,12 @@
         <v>203</v>
       </c>
       <c r="AP61" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B62" t="s">
         <v>43</v>
@@ -8611,7 +8602,7 @@
         <v>46</v>
       </c>
       <c r="F62" t="s">
-        <v>47</v>
+        <v>242</v>
       </c>
       <c r="G62" t="s">
         <v>48</v>
@@ -8710,7 +8701,7 @@
         <v>56</v>
       </c>
       <c r="AM62" t="s">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="AN62" t="s">
         <v>74</v>
@@ -8719,12 +8710,12 @@
         <v>77</v>
       </c>
       <c r="AP62" t="s">
-        <v>215</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="B63" t="s">
         <v>43</v>
@@ -8739,7 +8730,7 @@
         <v>46</v>
       </c>
       <c r="F63" t="s">
-        <v>247</v>
+        <v>47</v>
       </c>
       <c r="G63" t="s">
         <v>48</v>
@@ -8760,7 +8751,7 @@
         <v>78</v>
       </c>
       <c r="M63" t="s">
-        <v>54</v>
+        <v>243</v>
       </c>
       <c r="N63" t="s">
         <v>56</v>
@@ -8775,7 +8766,7 @@
         <v>58</v>
       </c>
       <c r="R63" t="s">
-        <v>248</v>
+        <v>79</v>
       </c>
       <c r="S63" t="s">
         <v>80</v>
@@ -8823,7 +8814,7 @@
         <v>72</v>
       </c>
       <c r="AH63" t="s">
-        <v>86</v>
+        <v>244</v>
       </c>
       <c r="AI63" t="s">
         <v>87</v>
@@ -8838,7 +8829,7 @@
         <v>56</v>
       </c>
       <c r="AM63" t="s">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c r="AN63" t="s">
         <v>87</v>
@@ -8847,12 +8838,12 @@
         <v>90</v>
       </c>
       <c r="AP63" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" t="s">
         <v>91</v>
@@ -8975,12 +8966,12 @@
         <v>110</v>
       </c>
       <c r="AP64" t="s">
-        <v>241</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B65" t="s">
         <v>91</v>
@@ -9094,7 +9085,7 @@
         <v>56</v>
       </c>
       <c r="AM65" t="s">
-        <v>246</v>
+        <v>73</v>
       </c>
       <c r="AN65" t="s">
         <v>74</v>
@@ -9103,12 +9094,12 @@
         <v>118</v>
       </c>
       <c r="AP65" t="s">
-        <v>103</v>
+        <v>199</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="B66" t="s">
         <v>120</v>
@@ -9159,7 +9150,7 @@
         <v>131</v>
       </c>
       <c r="R66" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
       <c r="S66" t="s">
         <v>60</v>
@@ -9231,12 +9222,12 @@
         <v>140</v>
       </c>
       <c r="AP66" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>205</v>
+        <v>119</v>
       </c>
       <c r="B67" t="s">
         <v>120</v>
@@ -9251,7 +9242,7 @@
         <v>123</v>
       </c>
       <c r="F67" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
       <c r="G67" t="s">
         <v>125</v>
@@ -9359,12 +9350,12 @@
         <v>146</v>
       </c>
       <c r="AP67" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="B68" t="s">
         <v>147</v>
@@ -9454,7 +9445,7 @@
         <v>66</v>
       </c>
       <c r="AE68" t="s">
-        <v>157</v>
+        <v>218</v>
       </c>
       <c r="AF68" t="s">
         <v>158</v>
@@ -9478,7 +9469,7 @@
         <v>159</v>
       </c>
       <c r="AM68" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="AN68" t="s">
         <v>60</v>
@@ -9487,12 +9478,12 @@
         <v>160</v>
       </c>
       <c r="AP68" t="s">
-        <v>62</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s">
         <v>161</v>
@@ -9615,12 +9606,12 @@
         <v>56</v>
       </c>
       <c r="AP69" t="s">
-        <v>204</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B70" t="s">
         <v>178</v>
@@ -9635,7 +9626,7 @@
         <v>181</v>
       </c>
       <c r="F70" t="s">
-        <v>79</v>
+        <v>240</v>
       </c>
       <c r="G70" t="s">
         <v>80</v>
@@ -9710,7 +9701,7 @@
         <v>66</v>
       </c>
       <c r="AE70" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF70" t="s">
         <v>116</v>
@@ -9743,12 +9734,12 @@
         <v>191</v>
       </c>
       <c r="AP70" t="s">
-        <v>214</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>221</v>
+        <v>42</v>
       </c>
       <c r="B71" t="s">
         <v>192</v>
@@ -9763,7 +9754,7 @@
         <v>194</v>
       </c>
       <c r="F71" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="G71" t="s">
         <v>131</v>
@@ -9784,7 +9775,7 @@
         <v>196</v>
       </c>
       <c r="M71" t="s">
-        <v>56</v>
+        <v>197</v>
       </c>
       <c r="N71" t="s">
         <v>56</v>
@@ -9799,7 +9790,7 @@
         <v>170</v>
       </c>
       <c r="R71" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="S71" t="s">
         <v>116</v>
@@ -9847,7 +9838,7 @@
         <v>72</v>
       </c>
       <c r="AH71" t="s">
-        <v>201</v>
+        <v>56</v>
       </c>
       <c r="AI71" t="s">
         <v>116</v>
@@ -9871,12 +9862,12 @@
         <v>203</v>
       </c>
       <c r="AP71" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="B72" t="s">
         <v>43</v>
@@ -9891,7 +9882,7 @@
         <v>46</v>
       </c>
       <c r="F72" t="s">
-        <v>47</v>
+        <v>247</v>
       </c>
       <c r="G72" t="s">
         <v>48</v>
@@ -9912,7 +9903,7 @@
         <v>53</v>
       </c>
       <c r="M72" t="s">
-        <v>54</v>
+        <v>248</v>
       </c>
       <c r="N72" t="s">
         <v>55</v>
@@ -9927,7 +9918,7 @@
         <v>58</v>
       </c>
       <c r="R72" t="s">
-        <v>251</v>
+        <v>59</v>
       </c>
       <c r="S72" t="s">
         <v>60</v>
@@ -9966,7 +9957,7 @@
         <v>69</v>
       </c>
       <c r="AE72" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="AF72" t="s">
         <v>71</v>
@@ -9999,12 +9990,12 @@
         <v>77</v>
       </c>
       <c r="AP72" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B73" t="s">
         <v>43</v>
@@ -10127,12 +10118,12 @@
         <v>90</v>
       </c>
       <c r="AP73" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>216</v>
+        <v>119</v>
       </c>
       <c r="B74" t="s">
         <v>91</v>
@@ -10147,7 +10138,7 @@
         <v>94</v>
       </c>
       <c r="F74" t="s">
-        <v>236</v>
+        <v>95</v>
       </c>
       <c r="G74" t="s">
         <v>96</v>
@@ -10246,7 +10237,7 @@
         <v>109</v>
       </c>
       <c r="AM74" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="AN74" t="s">
         <v>60</v>
@@ -10260,7 +10251,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="B75" t="s">
         <v>91</v>
@@ -10296,7 +10287,7 @@
         <v>111</v>
       </c>
       <c r="M75" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N75" t="s">
         <v>56</v>
@@ -10350,7 +10341,7 @@
         <v>114</v>
       </c>
       <c r="AE75" t="s">
-        <v>56</v>
+        <v>115</v>
       </c>
       <c r="AF75" t="s">
         <v>116</v>
@@ -10383,12 +10374,12 @@
         <v>118</v>
       </c>
       <c r="AP75" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
         <v>120</v>
@@ -10424,7 +10415,7 @@
         <v>126</v>
       </c>
       <c r="M76" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
       <c r="N76" t="s">
         <v>128</v>
@@ -10511,12 +10502,12 @@
         <v>140</v>
       </c>
       <c r="AP76" t="s">
-        <v>62</v>
+        <v>236</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B77" t="s">
         <v>120</v>
@@ -10531,7 +10522,7 @@
         <v>123</v>
       </c>
       <c r="F77" t="s">
-        <v>254</v>
+        <v>124</v>
       </c>
       <c r="G77" t="s">
         <v>125</v>
@@ -10552,7 +10543,7 @@
         <v>141</v>
       </c>
       <c r="M77" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="N77" t="s">
         <v>56</v>
@@ -10606,7 +10597,7 @@
         <v>136</v>
       </c>
       <c r="AE77" t="s">
-        <v>144</v>
+        <v>209</v>
       </c>
       <c r="AF77" t="s">
         <v>74</v>
@@ -10639,7 +10630,7 @@
         <v>146</v>
       </c>
       <c r="AP77" t="s">
-        <v>172</v>
+        <v>214</v>
       </c>
     </row>
     <row r="78">
@@ -10659,7 +10650,7 @@
         <v>149</v>
       </c>
       <c r="F78" t="s">
-        <v>115</v>
+        <v>251</v>
       </c>
       <c r="G78" t="s">
         <v>116</v>
@@ -10680,7 +10671,7 @@
         <v>151</v>
       </c>
       <c r="M78" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="N78" t="s">
         <v>153</v>
@@ -10767,12 +10758,12 @@
         <v>160</v>
       </c>
       <c r="AP78" t="s">
-        <v>103</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B79" t="s">
         <v>161</v>
@@ -10808,7 +10799,7 @@
         <v>166</v>
       </c>
       <c r="M79" t="s">
-        <v>255</v>
+        <v>167</v>
       </c>
       <c r="N79" t="s">
         <v>168</v>
@@ -10895,12 +10886,12 @@
         <v>56</v>
       </c>
       <c r="AP79" t="s">
-        <v>62</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B80" t="s">
         <v>178</v>
@@ -10999,7 +10990,7 @@
         <v>72</v>
       </c>
       <c r="AH80" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="AI80" t="s">
         <v>74</v>
@@ -11023,12 +11014,12 @@
         <v>191</v>
       </c>
       <c r="AP80" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="B81" t="s">
         <v>192</v>
@@ -11079,7 +11070,7 @@
         <v>170</v>
       </c>
       <c r="R81" t="s">
-        <v>115</v>
+        <v>56</v>
       </c>
       <c r="S81" t="s">
         <v>116</v>
@@ -11127,7 +11118,7 @@
         <v>72</v>
       </c>
       <c r="AH81" t="s">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="AI81" t="s">
         <v>116</v>
@@ -11151,7 +11142,7 @@
         <v>203</v>
       </c>
       <c r="AP81" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
